--- a/docs/assessments/hydro-station/05-detailed-risk-assessment.xlsx
+++ b/docs/assessments/hydro-station/05-detailed-risk-assessment.xlsx
@@ -1502,7 +1502,7 @@
     <row r="38" ht="46" customHeight="1" s="37">
       <c r="A38" s="59" t="inlineStr">
         <is>
-          <t>THE CONDITION ON ALL OF THIS. Six of the seven renotings hold ONLY because the hardwired overspeed trip is independent of every programmable device (assumption A-01, contracted as GC-2) and the gate closure-rate limit sits outside programmable logic (CRS-009). If A-01 is false, those six return to consequence 5, the Extreme band returns to 17, and Z-02 rises to SL-T 4. A-01 is the first thing to verify on site.</t>
+          <t>THE CONDITION ON ALL OF THIS. All six renotings hold ONLY because the hardwired overspeed trip is independent of every programmable device (assumption A-01, contracted as GC-2) and the gate closure-rate limit sits outside programmable logic (CRS-009). If A-01 is false, all six return to consequence 5, the Extreme band returns to 17, and Z-02 rises to SL-T 4. A-01 is the first thing to verify on site.</t>
         </is>
       </c>
     </row>
